--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_o_higgins.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_o_higgins.xlsx
@@ -394,10 +394,10 @@
         <v>16.40312884325992</v>
       </c>
       <c r="D2">
-        <v>63.27695915545676</v>
+        <v>63.27695915545677</v>
       </c>
       <c r="E2">
-        <v>20.31991200128331</v>
+        <v>20.31991200128332</v>
       </c>
     </row>
     <row r="3">
@@ -432,7 +432,7 @@
         <v>15.8788435061955</v>
       </c>
       <c r="D4">
-        <v>58.50160624139514</v>
+        <v>58.50160624139512</v>
       </c>
       <c r="E4">
         <v>25.61955025240936</v>
@@ -508,10 +508,10 @@
         <v>16.8603333872795</v>
       </c>
       <c r="D8">
-        <v>60.76064088040136</v>
+        <v>60.76064088040135</v>
       </c>
       <c r="E8">
-        <v>22.37902573231915</v>
+        <v>22.37902573231914</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         <v>16.17320986044085</v>
       </c>
       <c r="D12">
-        <v>62.63205947567497</v>
+        <v>62.63205947567496</v>
       </c>
       <c r="E12">
         <v>21.19473066388418</v>
@@ -603,7 +603,7 @@
         <v>15.60756652773325</v>
       </c>
       <c r="D13">
-        <v>60.87848669445335</v>
+        <v>60.87848669445336</v>
       </c>
       <c r="E13">
         <v>23.5139467778134</v>
@@ -676,7 +676,7 @@
         <v>117.760474601409</v>
       </c>
       <c r="C17">
-        <v>16.10245387784345</v>
+        <v>16.10245387784346</v>
       </c>
       <c r="D17">
         <v>64.93522001313511</v>
@@ -698,7 +698,7 @@
         <v>15.78740698564781</v>
       </c>
       <c r="D18">
-        <v>59.60379321854201</v>
+        <v>59.603793218542</v>
       </c>
       <c r="E18">
         <v>24.60879979581018</v>
@@ -758,7 +758,7 @@
         <v>57.7598385469223</v>
       </c>
       <c r="E21">
-        <v>25.67103935418769</v>
+        <v>25.67103935418768</v>
       </c>
     </row>
     <row r="22">
@@ -796,7 +796,7 @@
         <v>53.84794233899093</v>
       </c>
       <c r="E23">
-        <v>29.91164845384794</v>
+        <v>29.91164845384795</v>
       </c>
     </row>
     <row r="24">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>219.6834817012858</v>
+        <v>219.6834817012859</v>
       </c>
       <c r="C24">
         <v>13.51784997994384</v>
@@ -815,7 +815,7 @@
         <v>56.78566653295895</v>
       </c>
       <c r="E24">
-        <v>29.6964834870972</v>
+        <v>29.69648348709721</v>
       </c>
     </row>
     <row r="25">
@@ -828,7 +828,7 @@
         <v>126.9429308861485</v>
       </c>
       <c r="C25">
-        <v>16.73465470077267</v>
+        <v>16.73465470077266</v>
       </c>
       <c r="D25">
         <v>62.02188414838988</v>
@@ -850,7 +850,7 @@
         <v>15.96946564885496</v>
       </c>
       <c r="D26">
-        <v>58.62595419847328</v>
+        <v>58.62595419847329</v>
       </c>
       <c r="E26">
         <v>25.40458015267176</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>161.8078175895766</v>
+        <v>161.8078175895765</v>
       </c>
       <c r="C28">
         <v>16.60356949702542</v>
@@ -904,7 +904,7 @@
         <v>144.4064636420137</v>
       </c>
       <c r="C29">
-        <v>15.75365937239927</v>
+        <v>15.75365937239928</v>
       </c>
       <c r="D29">
         <v>61.49703823371028</v>
@@ -923,7 +923,7 @@
         <v>162.6701570680628</v>
       </c>
       <c r="C30">
-        <v>15.22154925087663</v>
+        <v>15.22154925087664</v>
       </c>
       <c r="D30">
         <v>60.0175326745298</v>
